--- a/investors/partners/PARTNER_WAR_ROOM.xlsx
+++ b/investors/partners/PARTNER_WAR_ROOM.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 DASHBOARD" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 PARTNER CRM'!$A$1:$Z$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 TARGET LIST'!$A$1:$M$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 PARTNER CRM'!$A$1:$Z$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 TARGET LIST'!$A$1:$M$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z75"/>
+  <dimension ref="A1:Z76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -626,9 +626,6 @@
           <t>Consultant Obstetrician, Clinical Lead for Hypertension in Pregnancy; Head of Midwifery; Digital Midwife</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -639,7 +636,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Service evaluation site; obstetric hypertension lead; 100–150 women</t>
@@ -650,13 +646,11 @@
           <t>No-fee evaluation, safety artefacts, co-authorship</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Via Health Innovation Oxford &amp; Thames Valley introduction; reference the BUMP evidence honestly</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -667,8 +661,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Public trust; verify current leads</t>
@@ -726,9 +718,6 @@
           <t>Professor of Primary Care Research leading the BP self-monitoring programme; senior researcher on BUMP</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -739,7 +728,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Evaluation partner; ethics sponsor; design of feasibility study</t>
@@ -750,13 +738,11 @@
           <t>Prospective data; co-investigator role; grant co-bids</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Email citing BUMP findings and asking to design what happens after the reading</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -767,8 +753,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Public academic group</t>
@@ -826,9 +810,6 @@
           <t>Director of NPEU; MBRRACE-UK lead</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -839,7 +820,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Methods advice; equity indicator alignment; later data linkage</t>
@@ -850,13 +830,11 @@
           <t>Continuous continuity data; equity reporting aligned to their framework</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Warm intro via Oxford; propose an equity-indicator workshop</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -867,8 +845,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Public body</t>
@@ -926,9 +902,6 @@
           <t>Clinical Director for Women's Services; Digital Midwife</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -939,7 +912,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Second evaluation site</t>
@@ -950,13 +922,11 @@
           <t>Evaluation, equity reporting</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Via Health Innovation Network South London</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -967,9 +937,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1022,9 +989,6 @@
           <t>Professor of Obstetrics/Maternal Health; Head of Department; Clinical Lead for Maternal Medicine</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1035,7 +999,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Research partner and site</t>
@@ -1046,13 +1009,11 @@
           <t>Cohort design; data; co-authorship</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Approach the department's maternal-health digital or pre-eclampsia lead with the equity design</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1063,9 +1024,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1118,9 +1076,6 @@
           <t>Consultant Obstetrician (Maternal Medicine); Head of Midwifery</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1131,7 +1086,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Site and research input</t>
@@ -1142,13 +1096,11 @@
           <t>Evaluation; data</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Via Imperial's innovation office</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1159,9 +1111,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1214,9 +1163,6 @@
           <t>Chief Medical Officer; Head of Midwifery</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1227,7 +1173,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Evaluation site</t>
@@ -1238,13 +1183,11 @@
           <t>Equity reporting; virtual ward</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Via Health Innovation West Midlands</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1255,9 +1198,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1310,9 +1250,6 @@
           <t>Director of Research; Consultant Obstetrician</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1323,7 +1260,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Site and research</t>
@@ -1334,13 +1270,11 @@
           <t>Evaluation; data</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Via the research centre director</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1351,9 +1285,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1406,9 +1337,6 @@
           <t>Clinical Head of Division (Obstetrics); Tommy's centre director</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1419,7 +1347,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Site; research input</t>
@@ -1430,13 +1357,11 @@
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Via Health Innovation Manchester</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1447,9 +1372,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1502,9 +1424,6 @@
           <t>Head of Midwifery; Digital Midwife</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1515,7 +1434,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Evaluation site</t>
@@ -1526,13 +1444,11 @@
           <t>Virtual ward</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Via Health Innovation Yorkshire &amp; Humber</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1543,9 +1459,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1598,9 +1511,6 @@
           <t>Institute Director; Professor of Maternal and Fetal Medicine</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1611,7 +1521,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Research partner</t>
@@ -1622,13 +1531,11 @@
           <t>Data; co-authorship</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Approach institute innovation lead</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1639,9 +1546,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1694,9 +1598,6 @@
           <t>Innovation Exchange Lead / Programme Manager (Maternity or Patient Safety)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1707,7 +1608,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Introductions to trusts; navigation support</t>
@@ -1718,13 +1618,11 @@
           <t>A well-governed evaluation for their portfolio</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Email with intended-use statement and evaluation concept; ask for the two-trust question</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1735,9 +1633,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1790,9 +1685,6 @@
           <t>Head of Innovation / Maternity Programme Lead</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1803,7 +1695,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Introductions</t>
@@ -1814,13 +1705,11 @@
           <t>Equity-focused evaluation</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Same as above</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1831,9 +1720,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1886,9 +1772,6 @@
           <t>Director of Innovation; Maternity lead</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1899,7 +1782,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Introductions; ICB route</t>
@@ -1910,13 +1792,11 @@
           <t>Evaluation; equity</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -1927,9 +1807,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -1982,9 +1859,6 @@
           <t>Innovation Exchange lead</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -1995,7 +1869,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Introductions</t>
@@ -2006,13 +1879,11 @@
           <t>Equity design</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2023,9 +1894,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -2078,9 +1946,6 @@
           <t>Head of Maternity Transformation / National Clinical Lead for Maternity Safety</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2091,7 +1956,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Alignment guidance; awareness</t>
@@ -2102,13 +1966,11 @@
           <t>Continuity layer aligned to MEWS; equity data</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Via HIN or NPEU introduction; never cold</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2119,8 +1981,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Do not claim endorsement</t>
@@ -2178,9 +2038,6 @@
           <t>Director of Research / Head of Maternal Health workstream</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2191,7 +2048,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Review of equity design; visibility</t>
@@ -2202,13 +2058,11 @@
           <t>Data on reach and response by ethnicity</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Email proposing an equity-indicator review</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2219,9 +2073,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -2274,9 +2125,6 @@
           <t>Director of Clinical Quality; Digital/Innovation lead</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2287,7 +2135,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Process review; events</t>
@@ -2298,13 +2145,11 @@
           <t>Alignment to guidance</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Approach via clinician partners</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2315,8 +2160,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>No endorsement claims</t>
@@ -2374,9 +2217,6 @@
           <t>Director for Professional Midwifery; Digital lead</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2387,7 +2227,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Midwifery workflow review; training content</t>
@@ -2398,13 +2237,11 @@
           <t>Training modules</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Email proposing a workflow review</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2415,9 +2252,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -2470,9 +2304,6 @@
           <t>Head of Research; Director of Research and Policy</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2483,7 +2314,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Review evaluation design; clinical champion introductions; community input</t>
@@ -2494,13 +2324,11 @@
           <t>Data sharing under governance; co-branded information content</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Email to Head of Research with the evaluation concept</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2511,9 +2339,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -2566,9 +2391,6 @@
           <t>Co-founders</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2579,7 +2401,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Equity design co-creation; community panel</t>
@@ -2590,13 +2411,11 @@
           <t>Paid advisory role; transparent equity reporting</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>LinkedIn note then call; offer paid involvement</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2607,8 +2426,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Public campaign founders</t>
@@ -2666,9 +2483,6 @@
           <t>Chief Executive; Head of Policy</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2679,7 +2493,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Consent and rights review</t>
@@ -2690,13 +2503,11 @@
           <t>Paid review; co-design</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2707,9 +2518,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -2762,9 +2570,6 @@
           <t>Director of Research</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2775,7 +2580,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Research funding; endorsement of study design</t>
@@ -2786,13 +2590,11 @@
           <t>Study proposal</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Apply when call opens</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2803,9 +2605,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -2858,9 +2657,6 @@
           <t>Chief Executive; Policy lead</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2871,7 +2667,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Postpartum module design</t>
@@ -2882,13 +2677,11 @@
           <t>Routing to services; data</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2899,9 +2692,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -2954,9 +2744,6 @@
           <t>Head of Research and Prevention</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -2967,7 +2754,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Safety and sensitivity review</t>
@@ -2978,13 +2764,11 @@
           <t>Content review</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -2995,9 +2779,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3050,9 +2831,6 @@
           <t>Clinical Director; Programme lead</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3063,7 +2841,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Standards alignment; minimum dataset</t>
@@ -3074,13 +2851,11 @@
           <t>Implementation feedback</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3091,9 +2866,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3146,9 +2918,6 @@
           <t>Director of Infrastructure / Perinatal data lead</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3159,7 +2928,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Cohort governance advice; TRE partnership</t>
@@ -3170,13 +2938,11 @@
           <t>New perinatal dataset</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3187,9 +2953,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3242,9 +3005,6 @@
           <t>Director; Head of Data</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3255,7 +3015,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Methods and linkage advice; site interest</t>
@@ -3266,13 +3025,11 @@
           <t>Digital continuity for a new sub-cohort</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3283,9 +3040,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3338,9 +3092,6 @@
           <t>Head of Partnerships / Product Director</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3351,7 +3102,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Interface specification; partner status</t>
@@ -3362,13 +3112,11 @@
           <t>Complementary home-monitoring; joint customers</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Approach after first trust LOI, through the trust's CCIO</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3379,9 +3127,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3434,9 +3179,6 @@
           <t>Commercial Director; Product lead</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3447,7 +3189,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Interface</t>
@@ -3458,13 +3199,11 @@
           <t>Complementary product</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Same as Clevermed</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3475,9 +3214,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3530,9 +3266,6 @@
           <t>Partnerships lead</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3543,7 +3276,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Interface</t>
@@ -3554,13 +3286,11 @@
           <t>Complementary product</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Same</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3571,9 +3301,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3626,9 +3353,6 @@
           <t>UK General Manager; Head of Partnerships</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3639,7 +3363,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>API access; per-test pricing; maternity pathway</t>
@@ -3650,13 +3373,11 @@
           <t>Maternity channel; case study</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Email with pathway description</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3667,9 +3388,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3722,9 +3440,6 @@
           <t>Medical Channel Manager UK; Head of Digital Health</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3735,7 +3450,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>SDK; loan devices; pricing</t>
@@ -3746,13 +3460,11 @@
           <t>Maternity channel; evidence</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Call medical channel team</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3763,9 +3475,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3818,9 +3527,6 @@
           <t>Head of B2B Health / Withings Health Solutions</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3831,7 +3537,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>SDK; devices</t>
@@ -3842,13 +3547,11 @@
           <t>Maternity use case</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Email B2B team</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3859,9 +3562,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -3914,9 +3614,6 @@
           <t>UK Sales Manager (medical)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -3927,7 +3624,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Devices; pricing</t>
@@ -3938,13 +3634,11 @@
           <t>Channel</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -3955,9 +3649,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4010,9 +3701,6 @@
           <t>Head of Health Innovation / Clinical Director for Women's Health</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4023,7 +3711,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Exploratory pilot of postpartum continuity as a benefit</t>
@@ -4034,13 +3721,11 @@
           <t>Evidence; product</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Via Bupa innovation team; after UK evidence</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4051,9 +3736,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4106,9 +3788,6 @@
           <t>Head of Propositions / Partnerships</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4119,7 +3798,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>Pilot conversation</t>
@@ -4130,13 +3808,11 @@
           <t>Continuity benefit</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4147,9 +3823,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4202,9 +3875,6 @@
           <t>Startup programme manager; Health industry lead</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4215,7 +3885,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Credits; architecture review; speech language support</t>
@@ -4226,13 +3895,11 @@
           <t>Reference case</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Apply to start-up programme; then industry lead</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4243,9 +3910,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4298,9 +3962,6 @@
           <t>Startup account manager; Healthcare BD</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4311,7 +3972,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Credits; solution architect time</t>
@@ -4322,13 +3982,11 @@
           <t>Reference</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4339,9 +3997,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4394,9 +4049,6 @@
           <t>Startup programme; Health partnerships</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4407,7 +4059,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Credits; language support</t>
@@ -4418,13 +4069,11 @@
           <t>Case study</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4435,9 +4084,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4490,9 +4136,6 @@
           <t>Head of Health, Vodafone Business; Vodacom health lead</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4503,7 +4146,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Zero-rated maternity messaging; IoT SIMs for devices</t>
@@ -4514,13 +4156,11 @@
           <t>Programme scale</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Email health vertical lead</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4531,9 +4171,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4586,9 +4223,6 @@
           <t>Head of Partnerships, Hospital Patient Monitoring / Venture lead</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4599,7 +4233,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>Interoperability; potential co-development later</t>
@@ -4610,13 +4243,11 @@
           <t>Continuity layer for their monitoring</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>After UK evidence; via Philips Ventures</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4627,9 +4258,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4682,9 +4310,6 @@
           <t>Head of Obstetrics research</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4695,7 +4320,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>EU evaluation partner (year 3)</t>
@@ -4706,13 +4330,11 @@
           <t>Data; evaluation</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4723,9 +4345,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4778,9 +4397,6 @@
           <t>Professor of Obstetrics/Epidemiology</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4791,7 +4407,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Methods; Nordic entry</t>
@@ -4802,13 +4417,11 @@
           <t>Data collaboration</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4819,9 +4432,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4874,9 +4484,6 @@
           <t>Managing Partner / GP</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4887,7 +4494,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Investment conversation (seed)</t>
@@ -4898,13 +4504,11 @@
           <t>Deal</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Via warm intro after LOI</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -4915,9 +4519,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -4970,9 +4571,6 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -4983,7 +4581,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Seed conversation</t>
@@ -4994,13 +4591,11 @@
           <t>Deal</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Warm intro</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5011,9 +4606,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5066,9 +4658,6 @@
           <t>Programme manager UK/Ireland</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5079,7 +4668,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Programme participation</t>
@@ -5090,13 +4678,11 @@
           <t>Case</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Apply if eligible</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5107,9 +4693,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5162,9 +4745,6 @@
           <t>Chief Innovation Officer / Innovation Fund lead</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5175,7 +4755,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>US partner conversations (year 3)</t>
@@ -5186,13 +4765,11 @@
           <t>Evidence; platform</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5203,9 +4780,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5258,9 +4832,6 @@
           <t>CEO / Head of Partnerships</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5271,7 +4842,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Benchmark; possible UK/Africa partnership</t>
@@ -5282,13 +4852,11 @@
           <t>Non-US markets</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Later, from strength</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5299,9 +4867,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5354,9 +4919,6 @@
           <t>Platform partnerships lead</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5367,7 +4929,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>Validation programme (year 3)</t>
@@ -5378,13 +4939,11 @@
           <t>Data model</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5395,9 +4954,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5450,9 +5006,6 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5463,7 +5016,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Seed conversation (US expansion)</t>
@@ -5474,13 +5026,11 @@
           <t>Deal</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5491,9 +5041,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5546,9 +5093,6 @@
           <t>Head of Partnerships / International</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5559,7 +5103,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>Partnership for continuity in non-US markets</t>
@@ -5570,13 +5113,11 @@
           <t>Platform</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5587,9 +5128,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5642,9 +5180,6 @@
           <t>Founder &amp; CEO; Head of Partnerships</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5655,7 +5190,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Complementarity partnership: continuity record and facility-side coordination beneath their programme</t>
@@ -5666,13 +5200,11 @@
           <t>Interoperability; facility workflow; evidence</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Founder-to-founder email proposing complementarity, not competition</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5683,9 +5215,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5738,9 +5267,6 @@
           <t>Managing Director; Director of Programmes (RMNCH)</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5751,7 +5277,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>Cohort of 500–2,000 women; community health workers</t>
@@ -5762,13 +5287,11 @@
           <t>Free platform; training; evaluation</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Email programme director</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5779,9 +5302,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5834,9 +5354,6 @@
           <t>Country Director Nigeria; Director of Digital Health</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5847,7 +5364,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>Technology-partner role in a funded programme</t>
@@ -5858,13 +5374,11 @@
           <t>Continuity layer; evaluation</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Email country office</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5875,9 +5389,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -5930,9 +5441,6 @@
           <t>Commissioner for Health; Permanent Secretary; PHC Board ES</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -5943,7 +5451,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Complementarity pilot with an implementer</t>
@@ -5954,13 +5461,11 @@
           <t>Continuity record; equity data</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Via implementer, never cold</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -5971,9 +5476,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6026,9 +5528,6 @@
           <t>Commissioner for Health; Programme Manager for maternal health</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6039,7 +5538,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>Re-scoped complementarity pilot</t>
@@ -6050,13 +5548,11 @@
           <t>Phased evidence pilot</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Reply with the re-scoped proposal</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6067,8 +5563,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>See FACTS_BASE</t>
@@ -6126,9 +5620,6 @@
           <t>Director of Community Health Services; Digital Health lead</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6139,7 +5630,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>Awareness; alignment</t>
@@ -6150,13 +5640,11 @@
           <t>Continuity layer for PHCs</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Via implementer</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6167,9 +5655,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6222,9 +5707,6 @@
           <t>President; Secretary General</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6235,7 +5717,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Clinical review; champions</t>
@@ -6246,13 +5727,11 @@
           <t>Alignment</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Email; conference</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6263,9 +5742,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6318,9 +5794,6 @@
           <t>Head of Digital Services / CSR (MTN Foundation)</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6331,7 +5804,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>Zero-rated messaging; USSD short code</t>
@@ -6342,13 +5814,11 @@
           <t>Programme scale; CSR</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Email foundation and digital services</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6359,9 +5829,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6414,9 +5881,6 @@
           <t>Head of Mobile Health / Partnerships</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6427,7 +5891,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Messaging; USSD</t>
@@ -6438,13 +5901,11 @@
           <t>Scale</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6455,9 +5916,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6510,9 +5968,6 @@
           <t>Head of Health, Safaricom / M-PESA partnerships</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6523,7 +5978,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Messaging; payments; distribution</t>
@@ -6534,13 +5988,11 @@
           <t>Kenya programme</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6551,9 +6003,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6606,9 +6055,6 @@
           <t>CEO; Director of Technology</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6619,7 +6065,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>Learning exchange; possible interoperability</t>
@@ -6630,13 +6075,11 @@
           <t>Continuity record for facility side</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Founder email</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6647,9 +6090,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6702,9 +6142,6 @@
           <t>CEO; Head of Health</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6715,7 +6152,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>Learning; interoperability</t>
@@ -6726,13 +6162,11 @@
           <t>Record layer</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6743,9 +6177,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6798,9 +6229,6 @@
           <t>Director of Digital Health / Country Director Nigeria</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6811,7 +6239,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>Digital-health advisory; programme partnership</t>
@@ -6822,13 +6249,11 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6839,9 +6264,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6894,9 +6316,6 @@
           <t>Chief of Health; Innovation Fund manager</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -6907,7 +6326,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>Programme alignment; innovation fund application</t>
@@ -6918,13 +6336,11 @@
           <t>Continuity tools</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Apply; programme contact via implementer</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -6935,9 +6351,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -6990,9 +6403,6 @@
           <t>Program Officer, MNCH / Digital Health</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7003,7 +6413,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Grant for low-resource validation (via partner)</t>
@@ -7014,13 +6423,11 @@
           <t>Evidence; cohort</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Via implementer or Grand Challenges routes</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7031,9 +6438,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7086,9 +6490,6 @@
           <t>Director, MSD for Mothers (UK/Africa lead)</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7099,7 +6500,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>Programme funding; introductions</t>
@@ -7110,13 +6510,11 @@
           <t>Continuity layer for funded programmes</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Email with complementarity to mDoc</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7127,9 +6525,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7182,9 +6577,6 @@
           <t>Program lead, Global Health</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7195,7 +6587,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>Application when call opens</t>
@@ -7206,13 +6597,11 @@
           <t>Evidence plan</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7223,9 +6612,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7278,9 +6664,6 @@
           <t>Programme Manager</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7291,7 +6674,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>Programme funding</t>
@@ -7302,13 +6684,11 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7319,9 +6699,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7374,9 +6751,6 @@
           <t>Director, Maternal &amp; Child Health</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7387,7 +6761,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>Programme funding via partners</t>
@@ -7398,13 +6771,11 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Via implementer</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7415,9 +6786,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7470,9 +6838,6 @@
           <t>Medical Affairs Lead, Women's Health; Head of Market Access UK</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7483,7 +6848,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>Pathway alignment; later co-development of a home-monitoring-to-test pathway</t>
@@ -7494,13 +6858,11 @@
           <t>Pathway data; adherence</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Medical affairs email after first LOI</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7511,9 +6873,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7566,9 +6925,6 @@
           <t>Medical Affairs, Women's Health</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7579,7 +6935,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>Programme partnership (postpartum)</t>
@@ -7590,13 +6945,11 @@
           <t>RWE</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7607,9 +6960,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7662,9 +7012,6 @@
           <t>Head of Medical Affairs UK; Partnerships</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Cold</t>
@@ -7675,7 +7022,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>Postpartum programme; RWE</t>
@@ -7686,13 +7032,11 @@
           <t>Cohort access under governance</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>RESEARCHED</t>
@@ -7703,9 +7047,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>Founder</t>
@@ -7727,8 +7068,128 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Dr Yusuf Shittu — independent (NHS Clinical Entrepreneur Programme)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Clinician founder / adviser</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2 Clinical</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Dr Yusuf Shittu</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>GP (MBBS MSc MRCGP); NHS Clinical Entrepreneur Programme; Imperial College London; healthcare designer and three-time founder</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>uk.linkedin.com — profile confirmed, URL slug TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Met in person</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Practising clinician who has built companies. Can say whether the record-keeping claim lands with clinicians or reads as admin. Knows the clinical safety officer market and the NHS innovation networks</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Honest product criticism; who should be the clinical safety officer; whether the Clinical Entrepreneur Programme has a route for a non-clinical founder; later, an introduction to a maternity clinician</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Nothing yet. Later: a named advisory role, paid, and equity if he takes it</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 — APPG on Black Maternal Health, Committee Room 10</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Connect on LinkedIn same evening quoting something specific he said; then a 20-minute call</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Met at the APPG. Do not ask him to be clinical safety officer yet — paid role with real liability. No email or phone held; do not guess one</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Met in person at a public parliamentary event, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Adviser (unpaid first call)</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Met in person and exchanged details at a professional event — he can opt out at any time</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z75"/>
+  <autoFilter ref="A1:Z76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7739,7 +7200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8063,7 +7524,6 @@
           <t>Diversity; London credibility</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8124,7 +7584,6 @@
           <t>Evidence; equity</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8185,7 +7644,6 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8246,7 +7704,6 @@
           <t>Diversity; specialist unit</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8307,7 +7764,6 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8368,7 +7824,6 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8429,7 +7884,6 @@
           <t>Scale</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8490,7 +7944,6 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8551,7 +8004,6 @@
           <t>Door-opener</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8612,7 +8064,6 @@
           <t>Door-opener</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8673,7 +8124,6 @@
           <t>Door-opener; ICB</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8734,7 +8184,6 @@
           <t>Door-opener</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8860,7 +8309,6 @@
           <t>Credibility on equity</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8986,7 +8434,6 @@
           <t>Midwife adoption</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9047,7 +8494,6 @@
           <t>Credibility; introductions</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9173,7 +8619,6 @@
           <t>Consent architecture credibility</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9234,7 +8679,6 @@
           <t>Funding</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9295,7 +8739,6 @@
           <t>Postpartum year design</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9356,7 +8799,6 @@
           <t>Safety design</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9417,7 +8859,6 @@
           <t>Interoperability credibility</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9478,7 +8919,6 @@
           <t>Data moat governance</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9539,7 +8979,6 @@
           <t>Data; diversity</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9600,7 +9039,6 @@
           <t>Interoperability</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9661,7 +9099,6 @@
           <t>Interoperability</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9722,7 +9159,6 @@
           <t>Interoperability</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9783,7 +9219,6 @@
           <t>Urine protein at home</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9844,7 +9279,6 @@
           <t>Validated input</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9905,7 +9339,6 @@
           <t>Validated input</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9966,7 +9399,6 @@
           <t>Alternative device</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10027,7 +9459,6 @@
           <t>Private payer; global</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10088,7 +9519,6 @@
           <t>Payer</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10149,7 +9579,6 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10210,7 +9639,6 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10271,7 +9699,6 @@
           <t>Voice/language</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -10332,7 +9759,6 @@
           <t>Distribution; low-resource</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10393,7 +9819,6 @@
           <t>Distribution</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10454,7 +9879,6 @@
           <t>EU entry</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10515,7 +9939,6 @@
           <t>Evidence</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10576,7 +9999,6 @@
           <t>Capital</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10637,7 +10059,6 @@
           <t>Capital</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10698,7 +10119,6 @@
           <t>Network</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10759,7 +10179,6 @@
           <t>US entry</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10820,7 +10239,6 @@
           <t>Learning; option</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10881,7 +10299,6 @@
           <t>US credibility</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10942,7 +10359,6 @@
           <t>Capital</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -11003,7 +10419,6 @@
           <t>Payer channel</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -11064,7 +10479,6 @@
           <t>Turns a competitor into a channel</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -11125,7 +10539,6 @@
           <t>Second market</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -11186,7 +10599,6 @@
           <t>Programme access</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -11247,7 +10659,6 @@
           <t>Scale</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11373,7 +10784,6 @@
           <t>National alignment</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -11434,7 +10844,6 @@
           <t>Legitimacy</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -11495,7 +10904,6 @@
           <t>Distribution</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11556,7 +10964,6 @@
           <t>Distribution</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -11617,7 +11024,6 @@
           <t>Kenya entry</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -11678,7 +11084,6 @@
           <t>Kenya; learning</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -11739,7 +11144,6 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -11800,7 +11204,6 @@
           <t>Programme access</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11861,7 +11264,6 @@
           <t>Scale; funding</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11922,7 +11324,6 @@
           <t>Funding; credibility</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11983,7 +11384,6 @@
           <t>Funding; credibility</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -12044,7 +11444,6 @@
           <t>Funding</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -12105,7 +11504,6 @@
           <t>Funding</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -12166,7 +11564,6 @@
           <t>Funding</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -12227,7 +11624,6 @@
           <t>Pathway credibility; commercial</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12288,7 +11684,6 @@
           <t>Postpartum</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12349,10 +11744,76 @@
           <t>Women's health</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Dr Yusuf Shittu — independent (NHS Clinical Entrepreneur Programme)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Clinician founder / adviser</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2 Clinical</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>A GP who has founded three companies and sits inside the NHS Clinical Entrepreneur Programme. The fastest honest read on whether the product is useful to clinicians</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Twenty minutes of criticism; a view on the clinical safety officer; a view on the Clinical Entrepreneur route</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Nothing yet. A paid advisory role later if he is interested</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>N/A — approach him directly</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Adviser, then possible clinical advisory board</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Already met in person at the APPG on 22 Sep 2026. Follow up the same evening, referencing what he actually said</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Clinical credibility, safety officer route, and a door into the NHS innovation networks</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>LinkedIn profile seen 22 Sep 2026; no contact details held</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M75"/>
+  <autoFilter ref="A1:M76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/investors/partners/PARTNER_WAR_ROOM.xlsx
+++ b/investors/partners/PARTNER_WAR_ROOM.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 DASHBOARD" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 PARTNER CRM'!$A$1:$Z$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 PARTNER CRM'!$A$1:$Z$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 TARGET LIST'!$A$1:$M$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z76"/>
+  <dimension ref="A1:Z77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7071,7 +7071,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dr Yusuf Shittu — independent (NHS Clinical Entrepreneur Programme)</t>
+          <t>MamaDoc (Dr Yusuf Shittu, co-founder and CEO)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Clinician founder / adviser</t>
+          <t>Community / education provider — and adjacent builder</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GP (MBBS MSc MRCGP); NHS Clinical Entrepreneur Programme; Imperial College London; healthcare designer and three-time founder</t>
+          <t>NHS GP (MBBS MSc MRCGP); co-founder and CEO of MamaDoc; NHS Clinical Entrepreneur Programme; Imperial College London</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Practising clinician who has built companies. Can say whether the record-keeping claim lands with clinicians or reads as admin. Knows the clinical safety officer market and the NHS innovation networks</t>
+          <t>Reaches and is trusted by the exact women in the national reports. Consumer front door to a clinical system. Also building in maternity, so treat as adjacent, not safe</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Honest product criticism; who should be the clinical safety officer; whether the Clinical Entrepreneur Programme has a route for a non-clinical founder; later, an introduction to a maternity clinician</t>
+          <t>A working relationship: MamaDoc as the woman-facing front door, MaternaLink as the clinical back end. Not his time as a safety officer — he runs his own company</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Nothing yet. Later: a named advisory role, paid, and equity if he takes it</t>
+          <t>Hospital-facing distribution he does not have; a clinical record his community content can sit against</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7149,17 +7149,14 @@
           <t>Connect on LinkedIn same evening quoting something specific he said; then a 20-minute call</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>1 Identified</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr">
         <is>
-          <t>Met at the APPG. Do not ask him to be clinical safety officer yet — paid role with real liability. No email or phone held; do not guess one</t>
+          <t>Co-founded with Dr Nimat, based in Leicester. WhatsApp-first support, antenatal classes, migrant and Black/Brown parents. DO NOT share roadmap, module list, pricing or the government strategy on a first meeting. He is not a competitor today but he is one feature away from being one</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7188,8 +7185,128 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MamaDoc (organisation)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Community / education provider</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2 Clinical</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Dr Yusuf Shittu (co-founder, CEO) and Dr Nimat (co-founder)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NHS GP; co-founders</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>mamadoc.co.uk</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Met a founder in person</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Trust and reach among Black, Brown and migrant parents. Antenatal classes and WhatsApp support. The demand side of the problem you are solving from the supply side</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>A referral or integration relationship; their read on what women actually ask for</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>A clinical system their community can be handed into; hospital routes they do not sell to</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 — met Dr Shittu at the APPG</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Read mamadoc.co.uk properly before any second conversation</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2 Contacted</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Adjacent builder. Partner first, but watch whether they move into the clinical record. Verify charity/company status at Companies House before proposing anything</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Met co-founder in person at a public parliamentary event, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Referral or integration partner</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Met in person at a professional event — opt out at any time</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z76"/>
+  <autoFilter ref="A1:Z77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/investors/partners/PARTNER_WAR_ROOM.xlsx
+++ b/investors/partners/PARTNER_WAR_ROOM.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 DASHBOARD" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 PARTNER CRM'!$A$1:$Z$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 PARTNER CRM'!$A$1:$Z$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 TARGET LIST'!$A$1:$M$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z77"/>
+  <dimension ref="A1:Z89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7266,14 +7266,11 @@
           <t>Read mamadoc.co.uk properly before any second conversation</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>2 Contacted</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
           <t>Adjacent builder. Partner first, but watch whether they move into the clinical record. Verify charity/company status at Companies House before proposing anything</t>
@@ -7305,8 +7302,1400 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Tommy's</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>National maternity charity</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>tommys.org</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>The largest UK pregnancy and baby charity. Funds research, runs clinics, sets what counts as evidence in maternity</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Content partnership; a view on the evidence plan; their Pregnancy Hub as a route to women</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Prospective data from a service evaluation; a named research question</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Approach: YES</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. Approach directly. They work with many organisations and this is not MamaDoc's to gatekeep</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>NCT (National Childbirth Trust)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>National maternity charity</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>nct.org.uk</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>The biggest antenatal education charity in the UK. Defines what parents expect antenatal support to look like</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>How they think about digital antenatal education; whether there is a content licence route</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Nothing yet. Later, reach into hospital pathways they do not touch</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Approach: YES</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. Approach directly, but not before you can say what you do in one sentence</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Birthrights</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Human rights in childbirth charity</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>birthrights.org.uk</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Legal and human-rights authority on maternity. Published the Systemic Racism inquiry. If they say your consent and records approach is right, that is worth more than a testimonial</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>A review of your consent wording and what a woman can see about herself</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>A product built so a woman can see her own record. That is their agenda, not just yours</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Approach: YES</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. Highest-credibility name on this list for your specific claim about records. Approach when the product is real enough to review</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Bliss</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Premature and sick babies charity</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>bliss.org.uk</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Owns the neonatal side. Relevant only when the newborn module is real</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Approach: LATER</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. Park until the newborn module exists. Do not approach early</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MAMA Academy</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Safer pregnancy charity</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>mamaacademy.org.uk</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Safer pregnancy charity known for maternity notes wallets and symptom awareness. Very close to your escalation argument</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Their view on what women actually miss and when</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Approach: YES</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. Small and practical. Likely to reply to a founder who asks well</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>For Baby's Sake</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Domestic abuse and early years charity</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>forbabyssake.org.uk</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Works with both parents where there is domestic abuse. MBRRACE January 2026 found 21% of the women who died had experienced domestic abuse</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>How a maternity record should handle a woman who is not safe at home</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Approach: YES</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. This is a real design problem you have not solved: who can see the record when the partner is the risk. Ask them, do not pitch</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Five X More</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Black maternal health campaign</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>fivexmore.org</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>The campaign that put Black maternal health in Parliament. Runs the Black Maternity Experiences survey. Connected to the APPG you attended</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Nothing, at first. Read their survey reports and use them properly</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Nothing yet. Never offer them a product</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Approach: CAREFUL</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. Do NOT approach as a vendor. Follow, read, cite them accurately. If you ever work together it will be because you were useful first</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>The Essential Baby Company (TEBC Ltd)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Equity training and consultancy</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2 Clinical</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>theessentialbabyco.com</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Reduces race-based inequality in maternity through training for clinicians and a patient involvement group. Commercial, so it understands selling into trusts</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>How they get trusts to pay for equity work; their patient involvement group as a design panel</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Paid work, potentially, rather than a favour</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Approach: YES</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. Note there are several similarly named entities at Companies House. Confirm which one before contracting</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>African Heritage Alliance / African Caribbean Centre</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Community organisation (Leicester)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>africanheritagealliance.org.uk</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Leicester community organisation, now running the African Caribbean Centre after a council asset transfer</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Approach: NO - VIA YUSUF</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. MamaDoc's home turf. Do not approach directly after meeting Yusuf</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Wesley Hall Community Centre</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Community centre (Leicester)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>wesleyhallcc.co.uk</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Leicester community hub in Highfields serving a largely Black and minority ethnic community. Runs antenatal and postnatal classes</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Approach: NO - VIA YUSUF</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. MamaDoc's home turf. Do not approach directly</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Leicester Mammas</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Peer support organisation (Leicester)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3 Voice</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>mammas.org.uk</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Peer breastfeeding support since 2008, about 50 peer supporters, over 1,200 women a year. Led by Sally Etheridge, lactation consultant</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Approach: NO - VIA YUSUF</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. MamaDoc's home turf. A model of peer support worth studying from a distance</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Leicester City Council</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Local authority / public health</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1 Foundational</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NOT YET IDENTIFIED</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>TO RESEARCH</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>leicester.gov.uk</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>EMAIL NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>PHONE NOT PUBLICLY AVAILABLE</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>A local authority backing a maternity organisation. Public health and Family Hubs are a real budget and a real buying route that is not the NHS</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Understand how a council commissions maternity support and what it pays</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Nothing yet</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Approach: STUDY, THEN OTHERS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1 Identified</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Listed publicly as a MamaDoc supporter, seen 22 Sep 2026. NO relationship with Vytalix. The interesting one. Councils buy faster than trusts. But approach a DIFFERENT council, not MamaDoc's</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Logo on mamadoc.co.uk supporter wall, 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Voice / content partner</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>No contact held. Use the organisation's own published enquiry route only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z77"/>
+  <autoFilter ref="A1:Z89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
